--- a/src/utils/sxsyzlzq/shijiesai/all4_count.xlsx
+++ b/src/utils/sxsyzlzq/shijiesai/all4_count.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\code\keyuanWeb\src\utils\sxsyzlzq\shijiesai\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
@@ -1434,7 +1439,7 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <f>SUM(B2:H2)</f>
+        <f t="shared" ref="I2:I65" si="0">SUM(B2:H2)</f>
         <v>10</v>
       </c>
     </row>
@@ -1446,7 +1451,7 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <f>SUM(B3:H3)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1461,7 +1466,7 @@
         <v>4</v>
       </c>
       <c r="I4">
-        <f>SUM(B4:H4)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
@@ -1473,7 +1478,7 @@
         <v>2</v>
       </c>
       <c r="I5">
-        <f>SUM(B5:H5)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -1488,7 +1493,7 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <f>SUM(B6:H6)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -1506,7 +1511,7 @@
         <v>3</v>
       </c>
       <c r="I7">
-        <f>SUM(B7:H7)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
@@ -1518,7 +1523,7 @@
         <v>2</v>
       </c>
       <c r="I8">
-        <f>SUM(B8:H8)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -1530,7 +1535,7 @@
         <v>2</v>
       </c>
       <c r="I9">
-        <f>SUM(B9:H9)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -1545,7 +1550,7 @@
         <v>3</v>
       </c>
       <c r="I10">
-        <f>SUM(B10:H10)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
@@ -1560,7 +1565,7 @@
         <v>1</v>
       </c>
       <c r="I11">
-        <f>SUM(B11:H11)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -1572,7 +1577,7 @@
         <v>7</v>
       </c>
       <c r="I12">
-        <f>SUM(B12:H12)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
@@ -1587,7 +1592,7 @@
         <v>2</v>
       </c>
       <c r="I13">
-        <f>SUM(B13:H13)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -1599,7 +1604,7 @@
         <v>1</v>
       </c>
       <c r="I14">
-        <f>SUM(B14:H14)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1611,7 +1616,7 @@
         <v>1</v>
       </c>
       <c r="I15">
-        <f>SUM(B15:H15)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1629,7 +1634,7 @@
         <v>3</v>
       </c>
       <c r="I16">
-        <f>SUM(B16:H16)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -1641,7 +1646,7 @@
         <v>1</v>
       </c>
       <c r="I17">
-        <f>SUM(B17:H17)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1653,7 +1658,7 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <f>SUM(B18:H18)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1665,7 +1670,7 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <f>SUM(B19:H19)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1677,7 +1682,7 @@
         <v>3</v>
       </c>
       <c r="I20">
-        <f>SUM(B20:H20)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -1689,7 +1694,7 @@
         <v>2</v>
       </c>
       <c r="I21">
-        <f>SUM(B21:H21)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -1701,7 +1706,7 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <f>SUM(B22:H22)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1713,7 +1718,7 @@
         <v>2</v>
       </c>
       <c r="I23">
-        <f>SUM(B23:H23)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -1728,7 +1733,7 @@
         <v>2</v>
       </c>
       <c r="I24">
-        <f>SUM(B24:H24)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -1740,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="I25">
-        <f>SUM(B25:H25)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1755,7 +1760,7 @@
         <v>2</v>
       </c>
       <c r="I26">
-        <f>SUM(B26:H26)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -1767,7 +1772,7 @@
         <v>1</v>
       </c>
       <c r="I27">
-        <f>SUM(B27:H27)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1779,7 +1784,7 @@
         <v>1</v>
       </c>
       <c r="I28">
-        <f>SUM(B28:H28)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1800,7 +1805,7 @@
         <v>2</v>
       </c>
       <c r="I29">
-        <f>SUM(B29:H29)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
@@ -1812,7 +1817,7 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <f>SUM(B30:H30)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1824,7 +1829,7 @@
         <v>2</v>
       </c>
       <c r="I31">
-        <f>SUM(B31:H31)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -1842,7 +1847,7 @@
         <v>2</v>
       </c>
       <c r="I32">
-        <f>SUM(B32:H32)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
@@ -1854,7 +1859,7 @@
         <v>1</v>
       </c>
       <c r="I33">
-        <f>SUM(B33:H33)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1866,7 +1871,7 @@
         <v>1</v>
       </c>
       <c r="I34">
-        <f>SUM(B34:H34)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1878,7 +1883,7 @@
         <v>1</v>
       </c>
       <c r="I35">
-        <f>SUM(B35:H35)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1893,7 +1898,7 @@
         <v>1</v>
       </c>
       <c r="I36">
-        <f>SUM(B36:H36)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -1905,7 +1910,7 @@
         <v>1</v>
       </c>
       <c r="I37">
-        <f>SUM(B37:H37)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1923,7 +1928,7 @@
         <v>2</v>
       </c>
       <c r="I38">
-        <f>SUM(B38:H38)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
@@ -1935,7 +1940,7 @@
         <v>2</v>
       </c>
       <c r="I39">
-        <f>SUM(B39:H39)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -1947,7 +1952,7 @@
         <v>1</v>
       </c>
       <c r="I40">
-        <f>SUM(B40:H40)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1959,7 +1964,7 @@
         <v>4</v>
       </c>
       <c r="I41">
-        <f>SUM(B41:H41)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -1971,7 +1976,7 @@
         <v>1</v>
       </c>
       <c r="I42">
-        <f>SUM(B42:H42)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1983,7 +1988,7 @@
         <v>1</v>
       </c>
       <c r="I43">
-        <f>SUM(B43:H43)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1998,7 +2003,7 @@
         <v>2</v>
       </c>
       <c r="I44">
-        <f>SUM(B44:H44)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -2010,7 +2015,7 @@
         <v>2</v>
       </c>
       <c r="I45">
-        <f>SUM(B45:H45)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2022,7 +2027,7 @@
         <v>4</v>
       </c>
       <c r="I46">
-        <f>SUM(B46:H46)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -2034,7 +2039,7 @@
         <v>1</v>
       </c>
       <c r="I47">
-        <f>SUM(B47:H47)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2049,7 +2054,7 @@
         <v>2</v>
       </c>
       <c r="I48">
-        <f>SUM(B48:H48)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -2067,7 +2072,7 @@
         <v>1</v>
       </c>
       <c r="I49">
-        <f>SUM(B49:H49)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
@@ -2079,7 +2084,7 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <f>SUM(B50:H50)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2091,7 +2096,7 @@
         <v>1</v>
       </c>
       <c r="I51">
-        <f>SUM(B51:H51)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2103,7 +2108,7 @@
         <v>1</v>
       </c>
       <c r="I52">
-        <f>SUM(B52:H52)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2115,7 +2120,7 @@
         <v>4</v>
       </c>
       <c r="I53">
-        <f>SUM(B53:H53)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -2130,7 +2135,7 @@
         <v>6</v>
       </c>
       <c r="I54">
-        <f>SUM(B54:H54)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
@@ -2151,7 +2156,7 @@
         <v>4</v>
       </c>
       <c r="I55">
-        <f>SUM(B55:H55)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
@@ -2172,7 +2177,7 @@
         <v>2</v>
       </c>
       <c r="I56">
-        <f>SUM(B56:H56)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
@@ -2190,7 +2195,7 @@
         <v>5</v>
       </c>
       <c r="I57">
-        <f>SUM(B57:H57)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
@@ -2202,7 +2207,7 @@
         <v>1</v>
       </c>
       <c r="I58">
-        <f>SUM(B58:H58)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2214,7 +2219,7 @@
         <v>3</v>
       </c>
       <c r="I59">
-        <f>SUM(B59:H59)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -2226,7 +2231,7 @@
         <v>2</v>
       </c>
       <c r="I60">
-        <f>SUM(B60:H60)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2241,7 +2246,7 @@
         <v>4</v>
       </c>
       <c r="I61">
-        <f>SUM(B61:H61)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -2253,7 +2258,7 @@
         <v>2</v>
       </c>
       <c r="I62">
-        <f>SUM(B62:H62)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2274,7 +2279,7 @@
         <v>2</v>
       </c>
       <c r="I63">
-        <f>SUM(B63:H63)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
@@ -2286,7 +2291,7 @@
         <v>1</v>
       </c>
       <c r="I64">
-        <f>SUM(B64:H64)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2304,7 +2309,7 @@
         <v>2</v>
       </c>
       <c r="I65">
-        <f>SUM(B65:H65)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
@@ -2316,7 +2321,7 @@
         <v>2</v>
       </c>
       <c r="I66">
-        <f>SUM(B66:H66)</f>
+        <f t="shared" ref="I66:I103" si="1">SUM(B66:H66)</f>
         <v>2</v>
       </c>
     </row>
@@ -2328,7 +2333,7 @@
         <v>1</v>
       </c>
       <c r="I67">
-        <f>SUM(B67:H67)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2343,7 +2348,7 @@
         <v>2</v>
       </c>
       <c r="I68">
-        <f>SUM(B68:H68)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -2355,7 +2360,7 @@
         <v>2</v>
       </c>
       <c r="I69">
-        <f>SUM(B69:H69)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -2367,7 +2372,7 @@
         <v>1</v>
       </c>
       <c r="I70">
-        <f>SUM(B70:H70)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2391,7 +2396,7 @@
         <v>1</v>
       </c>
       <c r="I71">
-        <f>SUM(B71:H71)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -2403,7 +2408,7 @@
         <v>1</v>
       </c>
       <c r="I72">
-        <f>SUM(B72:H72)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2415,7 +2420,7 @@
         <v>1</v>
       </c>
       <c r="I73">
-        <f>SUM(B73:H73)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2436,7 +2441,7 @@
         <v>2</v>
       </c>
       <c r="I74">
-        <f>SUM(B74:H74)</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
     </row>
@@ -2451,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="I75">
-        <f>SUM(B75:H75)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -2463,7 +2468,7 @@
         <v>1</v>
       </c>
       <c r="I76">
-        <f>SUM(B76:H76)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2475,7 +2480,7 @@
         <v>1</v>
       </c>
       <c r="I77">
-        <f>SUM(B77:H77)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2499,7 +2504,7 @@
         <v>1</v>
       </c>
       <c r="I78">
-        <f>SUM(B78:H78)</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
     </row>
@@ -2511,7 +2516,7 @@
         <v>1</v>
       </c>
       <c r="I79">
-        <f>SUM(B79:H79)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2529,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="I80">
-        <f>SUM(B80:H80)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -2541,7 +2546,7 @@
         <v>1</v>
       </c>
       <c r="I81">
-        <f>SUM(B81:H81)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2553,7 +2558,7 @@
         <v>2</v>
       </c>
       <c r="I82">
-        <f>SUM(B82:H82)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -2571,7 +2576,7 @@
         <v>4</v>
       </c>
       <c r="I83">
-        <f>SUM(B83:H83)</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
     </row>
@@ -2589,7 +2594,7 @@
         <v>3</v>
       </c>
       <c r="I84">
-        <f>SUM(B84:H84)</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
@@ -2604,7 +2609,7 @@
         <v>3</v>
       </c>
       <c r="I85">
-        <f>SUM(B85:H85)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -2619,7 +2624,7 @@
         <v>1</v>
       </c>
       <c r="I86">
-        <f>SUM(B86:H86)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -2631,7 +2636,7 @@
         <v>1</v>
       </c>
       <c r="I87">
-        <f>SUM(B87:H87)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2643,7 +2648,7 @@
         <v>2</v>
       </c>
       <c r="I88">
-        <f>SUM(B88:H88)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -2655,7 +2660,7 @@
         <v>1</v>
       </c>
       <c r="I89">
-        <f>SUM(B89:H89)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2667,7 +2672,7 @@
         <v>1</v>
       </c>
       <c r="I90">
-        <f>SUM(B90:H90)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2688,7 +2693,7 @@
         <v>2</v>
       </c>
       <c r="I91">
-        <f>SUM(B91:H91)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
@@ -2706,7 +2711,7 @@
         <v>3</v>
       </c>
       <c r="I92">
-        <f>SUM(B92:H92)</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
@@ -2718,7 +2723,7 @@
         <v>1</v>
       </c>
       <c r="I93">
-        <f>SUM(B93:H93)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2733,7 +2738,7 @@
         <v>4</v>
       </c>
       <c r="I94">
-        <f>SUM(B94:H94)</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
@@ -2745,7 +2750,7 @@
         <v>1</v>
       </c>
       <c r="I95">
-        <f>SUM(B95:H95)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2763,7 +2768,7 @@
         <v>2</v>
       </c>
       <c r="I96">
-        <f>SUM(B96:H96)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -2775,7 +2780,7 @@
         <v>1</v>
       </c>
       <c r="I97">
-        <f>SUM(B97:H97)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2787,7 +2792,7 @@
         <v>2</v>
       </c>
       <c r="I98">
-        <f>SUM(B98:H98)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -2799,7 +2804,7 @@
         <v>1</v>
       </c>
       <c r="I99">
-        <f>SUM(B99:H99)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2811,7 +2816,7 @@
         <v>1</v>
       </c>
       <c r="I100">
-        <f>SUM(B100:H100)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2832,7 +2837,7 @@
         <v>3</v>
       </c>
       <c r="I101">
-        <f>SUM(B101:H101)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
@@ -2844,7 +2849,7 @@
         <v>2</v>
       </c>
       <c r="I102">
-        <f>SUM(B102:H102)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -2856,7 +2861,7 @@
         <v>1</v>
       </c>
       <c r="I103">
-        <f>SUM(B103:H103)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2865,35 +2870,35 @@
         <v>111</v>
       </c>
       <c r="B106">
-        <f t="shared" ref="B106:I106" si="0">SUM(B2:B103)</f>
+        <f t="shared" ref="B106:I106" si="2">SUM(B2:B103)</f>
         <v>10</v>
       </c>
       <c r="C106">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="D106">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="E106">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="F106">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>38</v>
       </c>
       <c r="G106">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>80</v>
       </c>
       <c r="H106">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>160</v>
       </c>
       <c r="I106">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>320</v>
       </c>
     </row>

--- a/src/utils/sxsyzlzq/shijiesai/all4_count.xlsx
+++ b/src/utils/sxsyzlzq/shijiesai/all4_count.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="147">
   <si>
     <t>区服+名字</t>
   </si>
@@ -63,124 +63,265 @@
     <t>总数</t>
   </si>
   <si>
+    <t>157-段</t>
+  </si>
+  <si>
     <t>129-WZ(旧城之下)</t>
   </si>
   <si>
+    <t>144-zwy(九霄环佩)</t>
+  </si>
+  <si>
+    <t>146-KB</t>
+  </si>
+  <si>
+    <t>149-灰企鹅呆瓜</t>
+  </si>
+  <si>
+    <t>159-Jason（神樱）</t>
+  </si>
+  <si>
+    <t>146-江南</t>
+  </si>
+  <si>
+    <t>148-大核桃</t>
+  </si>
+  <si>
+    <t>137-No1.Mr</t>
+  </si>
+  <si>
+    <t>157-#</t>
+  </si>
+  <si>
+    <t>151-星空</t>
+  </si>
+  <si>
+    <t>145-SZH(老王)</t>
+  </si>
+  <si>
+    <t>148-请叫我阿奎</t>
+  </si>
+  <si>
+    <t>156-Tiao跳猪</t>
+  </si>
+  <si>
+    <t>150-开飞机的贝塔</t>
+  </si>
+  <si>
+    <t>133-神经蛙</t>
+  </si>
+  <si>
+    <t>137-鹰の一手</t>
+  </si>
+  <si>
+    <t>145-杜佳捷</t>
+  </si>
+  <si>
+    <t>154-吃鹿的于</t>
+  </si>
+  <si>
+    <t>151-suola</t>
+  </si>
+  <si>
+    <t>131-孔琦</t>
+  </si>
+  <si>
+    <t>130-随￥缘</t>
+  </si>
+  <si>
+    <t>134-木轩</t>
+  </si>
+  <si>
+    <t>137-神之千手(神之一手)</t>
+  </si>
+  <si>
+    <t>145-古月星辰</t>
+  </si>
+  <si>
+    <t>157-空泣</t>
+  </si>
+  <si>
+    <t>148-水煮肉片(数字经济)</t>
+  </si>
+  <si>
+    <t>142-异界淘金者</t>
+  </si>
+  <si>
+    <t>154-。马铃薯</t>
+  </si>
+  <si>
+    <t>133-叶小怪</t>
+  </si>
+  <si>
+    <t>133-抹小布</t>
+  </si>
+  <si>
+    <t>145-小黑</t>
+  </si>
+  <si>
+    <t>136-标</t>
+  </si>
+  <si>
+    <t>131-神经蛙</t>
+  </si>
+  <si>
+    <t>142-Limere</t>
+  </si>
+  <si>
+    <t>145-1</t>
+  </si>
+  <si>
+    <t>135-卡洛</t>
+  </si>
+  <si>
+    <t>148-12345</t>
+  </si>
+  <si>
+    <t>152-养乐多</t>
+  </si>
+  <si>
+    <t>136-miko</t>
+  </si>
+  <si>
+    <t>141-黑色香槟</t>
+  </si>
+  <si>
     <t>129-亚麻</t>
   </si>
   <si>
-    <t>130-随￥缘</t>
+    <t>131-朝闻道</t>
+  </si>
+  <si>
+    <t>137-未雨</t>
+  </si>
+  <si>
+    <t>132-长腿欧胖</t>
+  </si>
+  <si>
+    <t>134-跑</t>
+  </si>
+  <si>
+    <t>136-植物园园长</t>
+  </si>
+  <si>
+    <t>137-王熠</t>
+  </si>
+  <si>
+    <t>139-Lyric</t>
+  </si>
+  <si>
+    <t>144-草莓硬糖</t>
+  </si>
+  <si>
+    <t>147-没有nic</t>
+  </si>
+  <si>
+    <t>148-淘汰郎</t>
+  </si>
+  <si>
+    <t>158-nn</t>
+  </si>
+  <si>
+    <t>160-sky</t>
+  </si>
+  <si>
+    <t>133-杨豆豆</t>
+  </si>
+  <si>
+    <t>139-Sure</t>
+  </si>
+  <si>
+    <t>142-多幸运</t>
+  </si>
+  <si>
+    <t>145-[永恒]</t>
+  </si>
+  <si>
+    <t>145-明</t>
+  </si>
+  <si>
+    <t>159-叶随清风</t>
   </si>
   <si>
     <t>130-自然</t>
   </si>
   <si>
-    <t>131-朝闻道</t>
-  </si>
-  <si>
-    <t>131-孔琦</t>
-  </si>
-  <si>
-    <t>131-神经蛙</t>
-  </si>
-  <si>
     <t>132-YOKE</t>
   </si>
   <si>
-    <t>133-抹小布</t>
-  </si>
-  <si>
-    <t>133-神经蛙</t>
-  </si>
-  <si>
-    <t>133-杨豆豆</t>
-  </si>
-  <si>
-    <t>133-叶小怪</t>
+    <t>135-常世万法仙君</t>
+  </si>
+  <si>
+    <t>135-唔昂 王</t>
+  </si>
+  <si>
+    <t>136-0.o</t>
+  </si>
+  <si>
+    <t>137-菜的够吊</t>
+  </si>
+  <si>
+    <t>138-LEO</t>
+  </si>
+  <si>
+    <t>145-清风</t>
+  </si>
+  <si>
+    <t>145-夜的第七z</t>
+  </si>
+  <si>
+    <t>146-谢之求学者(念苍生)</t>
+  </si>
+  <si>
+    <t>148-白夜</t>
+  </si>
+  <si>
+    <t>150-朱</t>
+  </si>
+  <si>
+    <t>157-躺平的蛙</t>
+  </si>
+  <si>
+    <t>133-七月</t>
   </si>
   <si>
     <t>133-政杨</t>
   </si>
   <si>
+    <t>134-阿标</t>
+  </si>
+  <si>
     <t>134-高戈</t>
   </si>
   <si>
-    <t>134-木轩</t>
-  </si>
-  <si>
-    <t>134-跑</t>
-  </si>
-  <si>
     <t>134-破灭</t>
   </si>
   <si>
-    <t>135-常世万法仙君</t>
-  </si>
-  <si>
-    <t>135-卡洛</t>
-  </si>
-  <si>
-    <t>135-唔昂 王</t>
+    <t>135-梦入神机</t>
   </si>
   <si>
     <t>135-真理铁拳</t>
   </si>
   <si>
-    <t>136-0.o</t>
-  </si>
-  <si>
-    <t>136-miko</t>
-  </si>
-  <si>
     <t>136-OK（开尔文</t>
   </si>
   <si>
-    <t>136-标</t>
-  </si>
-  <si>
     <t>136-神经蛙</t>
   </si>
   <si>
-    <t>136-植物园园长</t>
-  </si>
-  <si>
-    <t>137-No1.Mr</t>
-  </si>
-  <si>
     <t>137-vwafew</t>
   </si>
   <si>
-    <t>137-菜的够吊</t>
-  </si>
-  <si>
-    <t>137-神之千手(神之一手)</t>
-  </si>
-  <si>
     <t>137-神之右手</t>
   </si>
   <si>
     <t>137-随便玩玩</t>
   </si>
   <si>
-    <t>137-王熠</t>
-  </si>
-  <si>
-    <t>137-未雨</t>
-  </si>
-  <si>
     <t>137-星星</t>
   </si>
   <si>
-    <t>137-鹰の一手</t>
-  </si>
-  <si>
-    <t>138-LEO</t>
-  </si>
-  <si>
-    <t>139-Lyric</t>
-  </si>
-  <si>
-    <t>139-Sure</t>
+    <t>138-V嗯哪K</t>
   </si>
   <si>
     <t>139-加禾影像|阿</t>
@@ -189,189 +330,87 @@
     <t>139-蒋凌峰</t>
   </si>
   <si>
-    <t>141-黑色香槟</t>
-  </si>
-  <si>
-    <t>142-Limere</t>
-  </si>
-  <si>
-    <t>142-多幸运</t>
+    <t>141-想吃夜宵</t>
   </si>
   <si>
     <t>142-老猫</t>
   </si>
   <si>
-    <t>142-异界淘金者</t>
-  </si>
-  <si>
-    <t>144-zwy(九霄环佩)</t>
-  </si>
-  <si>
-    <t>144-草莓硬糖</t>
-  </si>
-  <si>
     <t>144-神经蛙</t>
   </si>
   <si>
     <t>144-烟雨平生</t>
   </si>
   <si>
-    <t>145-[永恒]</t>
-  </si>
-  <si>
-    <t>145-1</t>
-  </si>
-  <si>
-    <t>145-杜佳捷</t>
-  </si>
-  <si>
-    <t>145-SZH(老王)</t>
-  </si>
-  <si>
-    <t>145-古月星辰</t>
-  </si>
-  <si>
     <t>145-九龙亦云</t>
   </si>
   <si>
-    <t>145-明</t>
-  </si>
-  <si>
-    <t>145-清风</t>
-  </si>
-  <si>
-    <t>145-小黑</t>
-  </si>
-  <si>
-    <t>145-夜的第七z</t>
-  </si>
-  <si>
-    <t>146-KB</t>
-  </si>
-  <si>
     <t>146-Thor</t>
   </si>
   <si>
-    <t>146-江南</t>
-  </si>
-  <si>
-    <t>146-谢之求学者(念苍生)</t>
-  </si>
-  <si>
-    <t>147-没有nic</t>
-  </si>
-  <si>
-    <t>148-12345</t>
-  </si>
-  <si>
-    <t>148-白夜</t>
+    <t>148-momo</t>
   </si>
   <si>
     <t>148-大锅</t>
   </si>
   <si>
-    <t>148-大核桃</t>
-  </si>
-  <si>
-    <t>148-momo</t>
-  </si>
-  <si>
     <t>148-攀攀</t>
   </si>
   <si>
-    <t>148-请叫我阿奎</t>
-  </si>
-  <si>
-    <t>148-水煮肉片(数字经济)</t>
-  </si>
-  <si>
-    <t>148-淘汰郎</t>
-  </si>
-  <si>
     <t>148-玩玩</t>
   </si>
   <si>
-    <t>149-灰企鹅呆瓜</t>
-  </si>
-  <si>
     <t>149-柒柒</t>
   </si>
   <si>
-    <t>150-开飞机的贝塔</t>
-  </si>
-  <si>
     <t>150-夏进</t>
   </si>
   <si>
-    <t>150-朱</t>
-  </si>
-  <si>
-    <t>151-suola</t>
-  </si>
-  <si>
-    <t>151-星空</t>
-  </si>
-  <si>
-    <t>152-养乐多</t>
-  </si>
-  <si>
-    <t>154-。马铃薯</t>
+    <t>152-狗托</t>
   </si>
   <si>
     <t>154-Felix</t>
   </si>
   <si>
-    <t>154-吃鹿的于</t>
-  </si>
-  <si>
     <t>154-江江江</t>
   </si>
   <si>
     <t>155-锋云</t>
   </si>
   <si>
-    <t>156-Tiao跳猪</t>
-  </si>
-  <si>
-    <t>157-#</t>
+    <t>156-啊啊啊啊</t>
   </si>
   <si>
     <t>157-动次打次</t>
   </si>
   <si>
-    <t>157-段</t>
-  </si>
-  <si>
     <t>157-寡王</t>
   </si>
   <si>
-    <t>157-空泣</t>
-  </si>
-  <si>
     <t>157-神经蛙</t>
   </si>
   <si>
-    <t>157-躺平的蛙</t>
-  </si>
-  <si>
     <t>157-我姓孟.</t>
   </si>
   <si>
-    <t>158-nn</t>
-  </si>
-  <si>
-    <t>159-Jason（神樱）</t>
-  </si>
-  <si>
-    <t>159-叶随清风</t>
-  </si>
-  <si>
-    <t>160-sky</t>
-  </si>
-  <si>
     <t>总数：</t>
   </si>
   <si>
+    <t>第十三届</t>
+  </si>
+  <si>
+    <t>zwy</t>
+  </si>
+  <si>
+    <t>KB</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>大核桃</t>
+  </si>
+  <si>
     <t>第十一届</t>
   </si>
   <si>
@@ -381,9 +420,6 @@
     <t>企鹅</t>
   </si>
   <si>
-    <t>zwy</t>
-  </si>
-  <si>
     <t>神经蛙</t>
   </si>
   <si>
@@ -402,9 +438,6 @@
     <t>星空</t>
   </si>
   <si>
-    <t>大核桃</t>
-  </si>
-  <si>
     <t>第七届</t>
   </si>
   <si>
@@ -415,9 +448,6 @@
   </si>
   <si>
     <t>No1.Mr</t>
-  </si>
-  <si>
-    <t>KB</t>
   </si>
   <si>
     <t>第五届</t>
@@ -1386,7 +1416,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I119"/>
+  <dimension ref="A1:I128"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1430,449 +1460,596 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <f t="shared" ref="I2:I65" si="0">SUM(B2:H2)</f>
-        <v>10</v>
+        <f>SUM(B2:H2)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="H3">
-        <v>1</v>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
       </c>
       <c r="I3">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B3:H3)</f>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="F4">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>SUM(B4:H4)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="H5">
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
         <v>2</v>
       </c>
       <c r="I5">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B5:H5)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>13</v>
       </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
       <c r="G6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B6:H6)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>14</v>
       </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
       <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H7">
         <v>3</v>
       </c>
       <c r="I7">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <f>SUM(B7:H7)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="G8">
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="H8">
         <v>2</v>
       </c>
       <c r="I8">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B8:H8)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>16</v>
       </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
       <c r="H9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B9:H9)</f>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>17</v>
       </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
       <c r="G10">
         <v>2</v>
       </c>
-      <c r="H10">
-        <v>3</v>
-      </c>
       <c r="I10">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>SUM(B10:H10)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="E11">
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+      <c r="G11">
         <v>1</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B11:H11)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>19</v>
       </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>3</v>
+      </c>
       <c r="H12">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I12">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f>SUM(B12:H12)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>20</v>
       </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
       <c r="G13">
         <v>4</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <f>SUM(B13:H13)</f>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>21</v>
       </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
       <c r="H14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B14:H14)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
         <v>22</v>
       </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
       <c r="H15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B15:H15)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>23</v>
       </c>
-      <c r="F16">
+      <c r="E16">
         <v>1</v>
       </c>
       <c r="G16">
         <v>2</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I16">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <f>SUM(B16:H16)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
         <v>24</v>
       </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
       <c r="G17">
         <v>1</v>
       </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
       <c r="I17">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B17:H17)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
         <v>25</v>
       </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
       <c r="H18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B18:H18)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
         <v>26</v>
       </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>3</v>
+      </c>
       <c r="H19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I19">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B19:H19)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
         <v>27</v>
       </c>
-      <c r="H20">
-        <v>3</v>
+      <c r="F20">
+        <v>2</v>
       </c>
       <c r="I20">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>SUM(B20:H20)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
         <v>28</v>
       </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>4</v>
+      </c>
       <c r="H21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I21">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B21:H21)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
         <v>29</v>
       </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
       <c r="H22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I22">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B22:H22)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
         <v>30</v>
       </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>4</v>
+      </c>
       <c r="H23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B23:H23)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
         <v>31</v>
       </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
       <c r="G24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I24">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>SUM(B24:H24)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
         <v>32</v>
       </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
       <c r="H25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B25:H25)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
         <v>33</v>
       </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
       <c r="G26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I26">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>SUM(B26:H26)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
         <v>34</v>
       </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
       <c r="H27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B27:H27)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
         <v>35</v>
       </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="I28">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B28:H28)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
         <v>36</v>
       </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
       <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>2</v>
+      </c>
+      <c r="I29">
+        <f>SUM(B29:H29)</f>
         <v>3</v>
-      </c>
-      <c r="G29">
-        <v>2</v>
-      </c>
-      <c r="I29">
-        <f t="shared" si="0"/>
-        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
         <v>37</v>
       </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
       <c r="H30">
         <v>1</v>
       </c>
       <c r="I30">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B30:H30)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
         <v>38</v>
       </c>
+      <c r="G31">
+        <v>4</v>
+      </c>
       <c r="H31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B31:H31)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
         <v>39</v>
       </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
       <c r="G32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I32">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>SUM(B32:H32)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
         <v>40</v>
       </c>
+      <c r="G33">
+        <v>2</v>
+      </c>
       <c r="H33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B33:H33)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
         <v>41</v>
       </c>
+      <c r="G34">
+        <v>2</v>
+      </c>
       <c r="H34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B34:H34)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1880,11 +2057,11 @@
         <v>42</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B35:H35)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1892,13 +2069,10 @@
         <v>43</v>
       </c>
       <c r="G36">
-        <v>1</v>
-      </c>
-      <c r="H36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36">
-        <f t="shared" si="0"/>
+        <f>SUM(B36:H36)</f>
         <v>2</v>
       </c>
     </row>
@@ -1906,42 +2080,45 @@
       <c r="A37" t="s">
         <v>44</v>
       </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
       <c r="H37">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I37">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B37:H37)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
         <v>45</v>
       </c>
-      <c r="F38">
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38">
         <v>3</v>
       </c>
-      <c r="G38">
-        <v>2</v>
-      </c>
-      <c r="H38">
-        <v>2</v>
-      </c>
       <c r="I38">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f>SUM(B38:H38)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
         <v>46</v>
       </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
       <c r="H39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I39">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B39:H39)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1951,45 +2128,57 @@
       <c r="G40">
         <v>1</v>
       </c>
+      <c r="H40">
+        <v>3</v>
+      </c>
       <c r="I40">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B40:H40)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
         <v>48</v>
       </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
       <c r="H41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I41">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>SUM(B41:H41)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
         <v>49</v>
       </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
       <c r="H42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I42">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B42:H42)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
         <v>50</v>
       </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B43:H43)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -2000,11 +2189,11 @@
         <v>1</v>
       </c>
       <c r="H44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>SUM(B44:H44)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -2012,10 +2201,13 @@
         <v>52</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
       </c>
       <c r="I45">
-        <f t="shared" si="0"/>
+        <f>SUM(B45:H45)</f>
         <v>2</v>
       </c>
     </row>
@@ -2023,23 +2215,23 @@
       <c r="A46" t="s">
         <v>53</v>
       </c>
-      <c r="H46">
-        <v>4</v>
+      <c r="G46">
+        <v>1</v>
       </c>
       <c r="I46">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>SUM(B46:H46)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
         <v>54</v>
       </c>
-      <c r="H47">
+      <c r="G47">
         <v>1</v>
       </c>
       <c r="I47">
-        <f t="shared" si="0"/>
+        <f>SUM(B47:H47)</f>
         <v>1</v>
       </c>
     </row>
@@ -2047,33 +2239,24 @@
       <c r="A48" t="s">
         <v>55</v>
       </c>
-      <c r="F48">
-        <v>1</v>
-      </c>
-      <c r="H48">
-        <v>2</v>
+      <c r="G48">
+        <v>1</v>
       </c>
       <c r="I48">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>SUM(B48:H48)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
         <v>56</v>
       </c>
-      <c r="D49">
-        <v>3</v>
-      </c>
-      <c r="E49">
-        <v>1</v>
-      </c>
       <c r="G49">
         <v>1</v>
       </c>
       <c r="I49">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>SUM(B49:H49)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -2084,7 +2267,7 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <f t="shared" si="0"/>
+        <f>SUM(B50:H50)</f>
         <v>1</v>
       </c>
     </row>
@@ -2092,11 +2275,11 @@
       <c r="A51" t="s">
         <v>58</v>
       </c>
-      <c r="H51">
+      <c r="G51">
         <v>1</v>
       </c>
       <c r="I51">
-        <f t="shared" si="0"/>
+        <f>SUM(B51:H51)</f>
         <v>1</v>
       </c>
     </row>
@@ -2104,11 +2287,11 @@
       <c r="A52" t="s">
         <v>59</v>
       </c>
-      <c r="H52">
+      <c r="G52">
         <v>1</v>
       </c>
       <c r="I52">
-        <f t="shared" si="0"/>
+        <f>SUM(B52:H52)</f>
         <v>1</v>
       </c>
     </row>
@@ -2116,12 +2299,12 @@
       <c r="A53" t="s">
         <v>60</v>
       </c>
-      <c r="H53">
-        <v>4</v>
+      <c r="G53">
+        <v>1</v>
       </c>
       <c r="I53">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>SUM(B53:H53)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -2131,72 +2314,45 @@
       <c r="G54">
         <v>1</v>
       </c>
-      <c r="H54">
-        <v>6</v>
-      </c>
       <c r="I54">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f>SUM(B54:H54)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" t="s">
         <v>62</v>
       </c>
-      <c r="E55">
-        <v>1</v>
-      </c>
-      <c r="F55">
-        <v>1</v>
-      </c>
       <c r="G55">
-        <v>2</v>
-      </c>
-      <c r="H55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I55">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <f>SUM(B55:H55)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" t="s">
         <v>63</v>
       </c>
-      <c r="E56">
-        <v>1</v>
-      </c>
-      <c r="F56">
-        <v>3</v>
-      </c>
-      <c r="G56">
-        <v>4</v>
-      </c>
       <c r="H56">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I56">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f>SUM(B56:H56)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" t="s">
         <v>64</v>
       </c>
-      <c r="F57">
-        <v>1</v>
-      </c>
-      <c r="G57">
-        <v>1</v>
-      </c>
       <c r="H57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I57">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f>SUM(B57:H57)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -2204,11 +2360,11 @@
         <v>65</v>
       </c>
       <c r="H58">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I58">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B58:H58)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -2216,11 +2372,11 @@
         <v>66</v>
       </c>
       <c r="H59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I59">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>SUM(B59:H59)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -2228,26 +2384,23 @@
         <v>67</v>
       </c>
       <c r="H60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I60">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B60:H60)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" t="s">
         <v>68</v>
       </c>
-      <c r="G61">
-        <v>2</v>
-      </c>
       <c r="H61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I61">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <f>SUM(B61:H61)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -2258,7 +2411,7 @@
         <v>2</v>
       </c>
       <c r="I62">
-        <f t="shared" si="0"/>
+        <f>SUM(B62:H62)</f>
         <v>2</v>
       </c>
     </row>
@@ -2266,21 +2419,12 @@
       <c r="A63" t="s">
         <v>70</v>
       </c>
-      <c r="C63">
-        <v>1</v>
-      </c>
-      <c r="E63">
-        <v>1</v>
-      </c>
-      <c r="F63">
-        <v>3</v>
-      </c>
-      <c r="G63">
+      <c r="H63">
         <v>2</v>
       </c>
       <c r="I63">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f>SUM(B63:H63)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -2288,29 +2432,23 @@
         <v>71</v>
       </c>
       <c r="H64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I64">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B64:H64)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" t="s">
         <v>72</v>
       </c>
-      <c r="D65">
-        <v>2</v>
-      </c>
-      <c r="F65">
-        <v>1</v>
-      </c>
       <c r="H65">
         <v>2</v>
       </c>
       <c r="I65">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>SUM(B65:H65)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -2321,7 +2459,7 @@
         <v>2</v>
       </c>
       <c r="I66">
-        <f t="shared" ref="I66:I103" si="1">SUM(B66:H66)</f>
+        <f>SUM(B66:H66)</f>
         <v>2</v>
       </c>
     </row>
@@ -2329,27 +2467,24 @@
       <c r="A67" t="s">
         <v>74</v>
       </c>
-      <c r="G67">
-        <v>1</v>
+      <c r="H67">
+        <v>2</v>
       </c>
       <c r="I67">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>SUM(B67:H67)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" t="s">
         <v>75</v>
       </c>
-      <c r="G68">
-        <v>1</v>
-      </c>
       <c r="H68">
         <v>2</v>
       </c>
       <c r="I68">
-        <f t="shared" si="1"/>
-        <v>3</v>
+        <f>SUM(B68:H68)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -2360,7 +2495,7 @@
         <v>2</v>
       </c>
       <c r="I69">
-        <f t="shared" si="1"/>
+        <f>SUM(B69:H69)</f>
         <v>2</v>
       </c>
     </row>
@@ -2369,35 +2504,23 @@
         <v>77</v>
       </c>
       <c r="H70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I70">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>SUM(B70:H70)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" t="s">
         <v>78</v>
       </c>
-      <c r="D71">
-        <v>1</v>
-      </c>
-      <c r="E71">
-        <v>1</v>
-      </c>
-      <c r="F71">
-        <v>2</v>
-      </c>
-      <c r="G71">
-        <v>5</v>
-      </c>
       <c r="H71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I71">
-        <f t="shared" si="1"/>
-        <v>10</v>
+        <f>SUM(B71:H71)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -2405,11 +2528,11 @@
         <v>79</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I72">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>SUM(B72:H72)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -2417,58 +2540,46 @@
         <v>80</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I73">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>SUM(B73:H73)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" t="s">
         <v>81</v>
       </c>
-      <c r="E74">
-        <v>1</v>
-      </c>
-      <c r="F74">
-        <v>1</v>
-      </c>
-      <c r="G74">
-        <v>4</v>
-      </c>
       <c r="H74">
         <v>2</v>
       </c>
       <c r="I74">
-        <f t="shared" si="1"/>
-        <v>8</v>
+        <f>SUM(B74:H74)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" t="s">
         <v>82</v>
       </c>
-      <c r="F75">
-        <v>1</v>
-      </c>
-      <c r="G75">
+      <c r="H75">
         <v>1</v>
       </c>
       <c r="I75">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f>SUM(B75:H75)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" t="s">
         <v>83</v>
       </c>
-      <c r="G76">
+      <c r="H76">
         <v>1</v>
       </c>
       <c r="I76">
-        <f t="shared" si="1"/>
+        <f>SUM(B76:H76)</f>
         <v>1</v>
       </c>
     </row>
@@ -2480,7 +2591,7 @@
         <v>1</v>
       </c>
       <c r="I77">
-        <f t="shared" si="1"/>
+        <f>SUM(B77:H77)</f>
         <v>1</v>
       </c>
     </row>
@@ -2488,24 +2599,12 @@
       <c r="A78" t="s">
         <v>85</v>
       </c>
-      <c r="C78">
-        <v>1</v>
-      </c>
-      <c r="D78">
-        <v>2</v>
-      </c>
-      <c r="F78">
-        <v>1</v>
-      </c>
-      <c r="G78">
-        <v>3</v>
-      </c>
       <c r="H78">
         <v>1</v>
       </c>
       <c r="I78">
-        <f t="shared" si="1"/>
-        <v>8</v>
+        <f>SUM(B78:H78)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -2516,7 +2615,7 @@
         <v>1</v>
       </c>
       <c r="I79">
-        <f t="shared" si="1"/>
+        <f>SUM(B79:H79)</f>
         <v>1</v>
       </c>
     </row>
@@ -2524,18 +2623,12 @@
       <c r="A80" t="s">
         <v>87</v>
       </c>
-      <c r="E80">
-        <v>1</v>
-      </c>
-      <c r="G80">
-        <v>2</v>
-      </c>
       <c r="H80">
         <v>1</v>
       </c>
       <c r="I80">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <f>SUM(B80:H80)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -2546,7 +2639,7 @@
         <v>1</v>
       </c>
       <c r="I81">
-        <f t="shared" si="1"/>
+        <f>SUM(B81:H81)</f>
         <v>1</v>
       </c>
     </row>
@@ -2555,77 +2648,59 @@
         <v>89</v>
       </c>
       <c r="H82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I82">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f>SUM(B82:H82)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" t="s">
         <v>90</v>
       </c>
-      <c r="F83">
-        <v>1</v>
-      </c>
-      <c r="G83">
-        <v>3</v>
-      </c>
       <c r="H83">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I83">
-        <f t="shared" si="1"/>
-        <v>8</v>
+        <f>SUM(B83:H83)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" t="s">
         <v>91</v>
       </c>
-      <c r="D84">
-        <v>1</v>
-      </c>
-      <c r="G84">
-        <v>3</v>
-      </c>
       <c r="H84">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I84">
-        <f t="shared" si="1"/>
-        <v>7</v>
+        <f>SUM(B84:H84)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" t="s">
         <v>92</v>
       </c>
-      <c r="G85">
-        <v>1</v>
-      </c>
       <c r="H85">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I85">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <f>SUM(B85:H85)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:9">
       <c r="A86" t="s">
         <v>93</v>
       </c>
-      <c r="F86">
-        <v>1</v>
-      </c>
       <c r="H86">
         <v>1</v>
       </c>
       <c r="I86">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f>SUM(B86:H86)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -2636,7 +2711,7 @@
         <v>1</v>
       </c>
       <c r="I87">
-        <f t="shared" si="1"/>
+        <f>SUM(B87:H87)</f>
         <v>1</v>
       </c>
     </row>
@@ -2644,12 +2719,12 @@
       <c r="A88" t="s">
         <v>95</v>
       </c>
-      <c r="F88">
-        <v>2</v>
+      <c r="H88">
+        <v>1</v>
       </c>
       <c r="I88">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f>SUM(B88:H88)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -2660,7 +2735,7 @@
         <v>1</v>
       </c>
       <c r="I89">
-        <f t="shared" si="1"/>
+        <f>SUM(B89:H89)</f>
         <v>1</v>
       </c>
     </row>
@@ -2672,7 +2747,7 @@
         <v>1</v>
       </c>
       <c r="I90">
-        <f t="shared" si="1"/>
+        <f>SUM(B90:H90)</f>
         <v>1</v>
       </c>
     </row>
@@ -2680,39 +2755,24 @@
       <c r="A91" t="s">
         <v>98</v>
       </c>
-      <c r="E91">
-        <v>1</v>
-      </c>
-      <c r="F91">
-        <v>1</v>
-      </c>
-      <c r="G91">
-        <v>1</v>
-      </c>
       <c r="H91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I91">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <f>SUM(B91:H91)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" t="s">
         <v>99</v>
       </c>
-      <c r="F92">
-        <v>5</v>
-      </c>
-      <c r="G92">
-        <v>1</v>
-      </c>
       <c r="H92">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I92">
-        <f t="shared" si="1"/>
-        <v>9</v>
+        <f>SUM(B92:H92)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -2723,7 +2783,7 @@
         <v>1</v>
       </c>
       <c r="I93">
-        <f t="shared" si="1"/>
+        <f>SUM(B93:H93)</f>
         <v>1</v>
       </c>
     </row>
@@ -2731,15 +2791,12 @@
       <c r="A94" t="s">
         <v>101</v>
       </c>
-      <c r="B94">
-        <v>5</v>
-      </c>
-      <c r="C94">
-        <v>4</v>
+      <c r="H94">
+        <v>1</v>
       </c>
       <c r="I94">
-        <f t="shared" si="1"/>
-        <v>9</v>
+        <f>SUM(B94:H94)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -2750,7 +2807,7 @@
         <v>1</v>
       </c>
       <c r="I95">
-        <f t="shared" si="1"/>
+        <f>SUM(B95:H95)</f>
         <v>1</v>
       </c>
     </row>
@@ -2758,18 +2815,12 @@
       <c r="A96" t="s">
         <v>103</v>
       </c>
-      <c r="F96">
-        <v>1</v>
-      </c>
-      <c r="G96">
-        <v>1</v>
-      </c>
       <c r="H96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I96">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <f>SUM(B96:H96)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -2780,7 +2831,7 @@
         <v>1</v>
       </c>
       <c r="I97">
-        <f t="shared" si="1"/>
+        <f>SUM(B97:H97)</f>
         <v>1</v>
       </c>
     </row>
@@ -2789,11 +2840,11 @@
         <v>105</v>
       </c>
       <c r="H98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I98">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f>SUM(B98:H98)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -2804,7 +2855,7 @@
         <v>1</v>
       </c>
       <c r="I99">
-        <f t="shared" si="1"/>
+        <f>SUM(B99:H99)</f>
         <v>1</v>
       </c>
     </row>
@@ -2812,11 +2863,11 @@
       <c r="A100" t="s">
         <v>107</v>
       </c>
-      <c r="G100">
+      <c r="H100">
         <v>1</v>
       </c>
       <c r="I100">
-        <f t="shared" si="1"/>
+        <f>SUM(B100:H100)</f>
         <v>1</v>
       </c>
     </row>
@@ -2824,21 +2875,12 @@
       <c r="A101" t="s">
         <v>108</v>
       </c>
-      <c r="C101">
-        <v>1</v>
-      </c>
-      <c r="E101">
-        <v>1</v>
-      </c>
-      <c r="F101">
-        <v>1</v>
-      </c>
       <c r="H101">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I101">
-        <f t="shared" si="1"/>
-        <v>6</v>
+        <f>SUM(B101:H101)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -2846,249 +2888,362 @@
         <v>109</v>
       </c>
       <c r="H102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I102">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f>SUM(B102:H102)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" t="s">
         <v>110</v>
       </c>
-      <c r="G103">
+      <c r="H103">
         <v>1</v>
       </c>
       <c r="I103">
-        <f t="shared" si="1"/>
+        <f>SUM(B103:H103)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" t="s">
+        <v>111</v>
+      </c>
+      <c r="H104">
+        <v>1</v>
+      </c>
+      <c r="I104">
+        <f>SUM(B104:H104)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105" t="s">
+        <v>112</v>
+      </c>
+      <c r="H105">
+        <v>1</v>
+      </c>
+      <c r="I105">
+        <f>SUM(B105:H105)</f>
         <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:9">
       <c r="A106" t="s">
-        <v>111</v>
-      </c>
-      <c r="B106">
-        <f t="shared" ref="B106:I106" si="2">SUM(B2:B103)</f>
-        <v>10</v>
-      </c>
-      <c r="C106">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="D106">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="E106">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="F106">
-        <f t="shared" si="2"/>
-        <v>38</v>
-      </c>
-      <c r="G106">
-        <f t="shared" si="2"/>
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="H106">
-        <f t="shared" si="2"/>
-        <v>160</v>
+        <v>1</v>
       </c>
       <c r="I106">
-        <f t="shared" si="2"/>
-        <v>320</v>
+        <f>SUM(B106:H106)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
+      <c r="A107" t="s">
+        <v>114</v>
+      </c>
+      <c r="H107">
+        <v>1</v>
+      </c>
+      <c r="I107">
+        <f>SUM(B107:H107)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="A108" t="s">
+        <v>115</v>
+      </c>
+      <c r="H108">
+        <v>1</v>
+      </c>
+      <c r="I108">
+        <f>SUM(B108:H108)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:9">
-      <c r="B109" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D109" s="1" t="s">
+      <c r="A109" t="s">
+        <v>116</v>
+      </c>
+      <c r="H109">
+        <v>1</v>
+      </c>
+      <c r="I109">
+        <f>SUM(B109:H109)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" t="s">
+        <v>117</v>
+      </c>
+      <c r="H110">
+        <v>1</v>
+      </c>
+      <c r="I110">
+        <f>SUM(B110:H110)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="A111" t="s">
+        <v>118</v>
+      </c>
+      <c r="H111">
+        <v>1</v>
+      </c>
+      <c r="I111">
+        <f>SUM(B111:H111)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
+      <c r="A114" t="s">
+        <v>119</v>
+      </c>
+      <c r="B114">
+        <f t="shared" ref="B114:I114" si="0">SUM(B2:B111)</f>
+        <v>11</v>
+      </c>
+      <c r="C114">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="D114">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="E114">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F114">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="G114">
+        <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+      <c r="H114">
+        <f t="shared" si="0"/>
+        <v>176</v>
+      </c>
+      <c r="I114">
+        <f t="shared" si="0"/>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
+      <c r="B117" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E109" s="1" t="s">
+      <c r="E117" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
-      <c r="A110" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B110" t="s">
-        <v>113</v>
-      </c>
-      <c r="C110" t="s">
-        <v>114</v>
-      </c>
-      <c r="D110" t="s">
-        <v>115</v>
-      </c>
-      <c r="E110" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9">
-      <c r="A111" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B111" t="s">
-        <v>113</v>
-      </c>
-      <c r="C111" t="s">
-        <v>118</v>
-      </c>
-      <c r="D111" t="s">
-        <v>114</v>
-      </c>
-      <c r="E111" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9">
-      <c r="A112" s="1" t="s">
+    <row r="118" spans="1:9">
+      <c r="A118" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B112" t="s">
-        <v>113</v>
-      </c>
-      <c r="C112" t="s">
-        <v>118</v>
-      </c>
-      <c r="D112" t="s">
+      <c r="B118" t="s">
         <v>121</v>
       </c>
-      <c r="E112" t="s">
+      <c r="C118" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="113" spans="1:5">
-      <c r="A113" s="1" t="s">
+      <c r="D118" t="s">
         <v>123</v>
       </c>
-      <c r="B113" t="s">
-        <v>113</v>
-      </c>
-      <c r="C113" t="s">
-        <v>118</v>
-      </c>
-      <c r="D113" t="s">
-        <v>122</v>
-      </c>
-      <c r="E113" t="s">
+      <c r="E118" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
-      <c r="A114" s="1" t="s">
+    <row r="119" spans="1:9">
+      <c r="A119" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B114" t="s">
-        <v>118</v>
-      </c>
-      <c r="C114" t="s">
-        <v>113</v>
-      </c>
-      <c r="D114" t="s">
+      <c r="B119" t="s">
         <v>126</v>
-      </c>
-      <c r="E114" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
-      <c r="A115" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B115" t="s">
-        <v>118</v>
-      </c>
-      <c r="C115" t="s">
-        <v>113</v>
-      </c>
-      <c r="D115" t="s">
-        <v>129</v>
-      </c>
-      <c r="E115" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
-      <c r="A116" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B116" t="s">
-        <v>118</v>
-      </c>
-      <c r="C116" t="s">
-        <v>131</v>
-      </c>
-      <c r="D116" t="s">
-        <v>114</v>
-      </c>
-      <c r="E116" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
-      <c r="A117" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B117" t="s">
-        <v>113</v>
-      </c>
-      <c r="C117" t="s">
-        <v>118</v>
-      </c>
-      <c r="D117" t="s">
-        <v>129</v>
-      </c>
-      <c r="E117" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5">
-      <c r="A118" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B118" t="s">
-        <v>118</v>
-      </c>
-      <c r="C118" t="s">
-        <v>113</v>
-      </c>
-      <c r="D118" t="s">
-        <v>115</v>
-      </c>
-      <c r="E118" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5">
-      <c r="A119" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B119" t="s">
-        <v>118</v>
       </c>
       <c r="C119" t="s">
         <v>127</v>
       </c>
       <c r="D119" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E119" t="s">
-        <v>113</v>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
+      <c r="A120" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B120" t="s">
+        <v>126</v>
+      </c>
+      <c r="C120" t="s">
+        <v>130</v>
+      </c>
+      <c r="D120" t="s">
+        <v>127</v>
+      </c>
+      <c r="E120" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
+      <c r="A121" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B121" t="s">
+        <v>126</v>
+      </c>
+      <c r="C121" t="s">
+        <v>130</v>
+      </c>
+      <c r="D121" t="s">
+        <v>133</v>
+      </c>
+      <c r="E121" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
+      <c r="A122" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B122" t="s">
+        <v>126</v>
+      </c>
+      <c r="C122" t="s">
+        <v>130</v>
+      </c>
+      <c r="D122" t="s">
+        <v>124</v>
+      </c>
+      <c r="E122" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
+      <c r="A123" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B123" t="s">
+        <v>130</v>
+      </c>
+      <c r="C123" t="s">
+        <v>126</v>
+      </c>
+      <c r="D123" t="s">
+        <v>137</v>
+      </c>
+      <c r="E123" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
+      <c r="A124" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B124" t="s">
+        <v>130</v>
+      </c>
+      <c r="C124" t="s">
+        <v>126</v>
+      </c>
+      <c r="D124" t="s">
+        <v>139</v>
+      </c>
+      <c r="E124" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
+      <c r="A125" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B125" t="s">
+        <v>130</v>
+      </c>
+      <c r="C125" t="s">
+        <v>141</v>
+      </c>
+      <c r="D125" t="s">
+        <v>127</v>
+      </c>
+      <c r="E125" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
+      <c r="A126" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B126" t="s">
+        <v>126</v>
+      </c>
+      <c r="C126" t="s">
+        <v>130</v>
+      </c>
+      <c r="D126" t="s">
+        <v>139</v>
+      </c>
+      <c r="E126" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
+      <c r="A127" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B127" t="s">
+        <v>130</v>
+      </c>
+      <c r="C127" t="s">
+        <v>126</v>
+      </c>
+      <c r="D127" t="s">
+        <v>121</v>
+      </c>
+      <c r="E127" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
+      <c r="A128" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B128" t="s">
+        <v>130</v>
+      </c>
+      <c r="C128" t="s">
+        <v>122</v>
+      </c>
+      <c r="D128" t="s">
+        <v>121</v>
+      </c>
+      <c r="E128" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:I97">
-    <sortCondition ref="A2"/>
+  <sortState ref="A2:I111">
+    <sortCondition ref="B2" descending="1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
